--- a/tabelas_classes_excel/Tabela_3-17_O_Ranger.xlsx
+++ b/tabelas_classes_excel/Tabela_3-17_O_Ranger.xlsx
@@ -922,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -975,31 +975,6 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1011,122 +986,182 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bônus Base de</t>
+          <t>Nível</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bônus Base de Ataque</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fortitude</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reflexos</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vontade</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Especial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nível</t>
+          <t>1°</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fortitude</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reflexos</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vontade Especial</t>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1° inimigo predileto, rastrear, empatia com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ataque</t>
+          <t>2°</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Estilo de Combate</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1°</t>
+          <t>3°</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>+0</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1° inimigo predileto, rastrear, empatia com</t>
+          <t>Tolerância</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2°</t>
+          <t>4°</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Estilo de Combate</t>
+          <t>Companheiro animal</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3°</t>
+          <t>5°</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1136,93 +1171,93 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tolerância</t>
+          <t>2° inimigo predileto</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4°</t>
+          <t>6°</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6/+1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Companheiro animal</t>
+          <t>Estilo de Combate Aprimorado</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5°</t>
+          <t>7°</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>+7/+2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2° inimigo predileto</t>
+          <t>Caminho da floresta</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6°</t>
+          <t>8°</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+8/+3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1232,93 +1267,93 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Estilo de Combate Aprimorado</t>
+          <t>Rastreador Eficaz</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7°</t>
+          <t>9°</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+7/+2</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Caminho da floresta</t>
+          <t>Evasão</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8°</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+8/+3</t>
+          <t>+10/+5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rastreador Eficaz</t>
+          <t>3° inimigo predileto</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9°</t>
+          <t>11°</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+11/+6/+1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1328,93 +1363,93 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Evasão</t>
+          <t>Domínio do Estilo de Combate</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10°</t>
+          <t>12°</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+10/+5</t>
+          <t>+12/+7/+2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3° inimigo predileto</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11°</t>
+          <t>13°</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>+11/+6/+1</t>
+          <t>+13/+8/+3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Domínio do Estilo de Combate</t>
+          <t>Camuflagem</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12°</t>
+          <t>14°</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>+12/+7/+2</t>
+          <t>+14/+9/+4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1431,59 +1466,59 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13°</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>+13/+8/+3</t>
+          <t>+15/+10/+5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Camuflagem</t>
+          <t>4° inimigo predileto</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14°</t>
+          <t>16°</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>+14/+9/+4</t>
+          <t>+16/+11/+6/+1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1495,22 +1530,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>17°</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>+15/+10/+5</t>
+          <t>+17/+12/+7/+2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1520,34 +1555,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4° inimigo predileto</t>
+          <t>Mimetismo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16°</t>
+          <t>18°</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+16/+11/+6/+1</t>
+          <t>+18/+13/+8/+3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1559,54 +1594,54 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17°</t>
+          <t>19°</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>+17/+12/+7/+2</t>
+          <t>+19/+14/+9/+4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mimetismo</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18°</t>
+          <t>20°</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+18/+13/+8/+3</t>
+          <t>+20/+15/+10/+5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1616,476 +1651,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>19°</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>+19/+14/+9/+4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20°</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>+20/+15/+10/+5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
           <t>5° inimigo predileto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>de inimigo e seu treinamento nas técnicas corretas para combatê-lo, o ranger recebe</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Para usar a empatia com a n</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>+2 de bônus nos testes de Blefar, Ouvir, Sentir Motivação, Observar e Sobrevivência</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>estudar um ao outro – ou seja,</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>realizados contra essas criaturas. Da mesma forma, ele recebe +2 de bônus nas jogadas</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>normais de iluminação. Normalme</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>de ataque e dano contra essas criaturas.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1 minuto; no entanto, semelhant</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>No 5° nível, e a cada cinco níveis subseqüentes (10°, 15° e 20° nível), o ranger</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ou menos tempo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>poderá escolher um novo inimigo predileto entre as espécies da tabela. Além disso,</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Um ranger também pode usar</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>nesse mesmo intervalo, o bônus contra qualquer inimigo predileto (incluindo o tipo</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>com Inteligência 1 ou 2 (como u</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>recém-adquirido, se o personagem desejar) aumenta em 2 pontos. Por exemplo, um</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>penalidade no teste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ranger do 5° nível teria dois inimigos prediletos. Contra um deles, o ranger recebe +4</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Estilo de Combate (Ext): N</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>de bônus nos testes de Blefar, Ouvir, Sentir Motivação, Observar e Sobrevivência e</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>combate que definirá sua carrei</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>nas jogadas de ataque e dano; contra a segunda espécie, ele recebe +2 de bônus nos</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>escolha afetará as característi</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>mesmos testes. No 10° nível, ele terá 3 inimigos prediletos e receberá +2 de bônus</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>nenhuma maneira sua escolha de</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adicional, que poderia ser designado para qualquer um dos seus inimigos prediletos.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Se o ranger escolher Arquear</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Portanto, seus bônus poderiam ser +4,+4,+2 ou +6,+2,+2.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>mesmo que não atenda aos pré-re</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Se o ranger escolher humanóides ou extra-planares como inimigos prediletos,</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Se o ranger escolher Comba</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ele deverá selecionar um subtipo apropriado, conforme indicado na tabela. Quando</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>o talento Combater com Duas Arm</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>uma determinada criatura estiver relacionada com mais de uma categoria de inimi-</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>normais.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>go predileto (por exemplo, os diabos são extra-planares Malignos e extra-planares</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Os benefícios do estilo es</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Leais), os bônus não se acumulam; ele simplesmente utiliza os modificadores mais</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>estiver sem armadura ou usando</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>elevados. Consulte o Livro dos Monstros para obter mais informações sobre os tipos</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>de seu estilo de combate quando</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>de criaturas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Tolerância: No 3° nível, um</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Rastrear: Um ranger recebe o talento Rastrear como um talento adicional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Empatia com a Natureza (Ext): Um ranger é capaz de usar linguagem corpo-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Companheiro Animal (Ext):</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ral, vocalizações e comportamentos para aprimorar a atitude de um animal (como</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>animal, selecionado da seguinte</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>um urso ou lagarto). Essa habilidade funciona da mesma forma que</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>um teste de</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cavalo (leve ou pesado), coruja</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Diplomacia realizado para aprimorar a atitude de uma pessoa (veja Capítulo 4:</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>quena ou Média). Caso a campanh</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Perícias). O ranger faz um teste especial com 1d20 + nível de ranger + modificador</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>região aquática, adicione as se</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>de Carisma para determinar o resultado do teste de empatia com a natureza. Um</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>lula e tubarão Médio. Esse anim</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>animal doméstico comum terá a atitude inicial Indiferente, enquanto os animais</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>ranger em suas aventuras confor</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>selvagens geralmente serão Pouco Amistosos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>criatura aquática não poderia s</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>escolhida por rangers terrestre</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>dos casos, o companheiro animal</t>
         </is>
       </c>
     </row>
